--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -66,12 +66,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -485,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -591,8 +592,10 @@
           <t>Last Synced Log Id</t>
         </is>
       </c>
-    </row>
-    <row r="9"/>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -911,7 +914,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>010_account_load.sql</t>
+          <t>040_account_load.sql</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -921,8 +924,40 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:24:25.093588</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:24:33.864677</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #1 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>500</v>
+      </c>
+      <c r="M20" t="n">
+        <v>500</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -931,9 +966,9 @@
           <t>Load</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Contact</t>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>050_contact_load.sql</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -943,58 +978,107 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Not Started</t>
-        </is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:25:23.666209</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:25:38.022160</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #2 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>738</v>
+      </c>
+      <c r="M21" t="n">
+        <v>738</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>060_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:26:17.038396</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-07-10T22:26:44.202428</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #3 (insert, 2 job(s)).</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>372</v>
+      </c>
+      <c r="M22" t="n">
+        <v>372</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Post-Migration Steps</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Salesforce Config Changes</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Re-enable Email Deliverability to its normal setting</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1004,7 +1088,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
+          <t>Re-enable Email Deliverability to its normal setting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1031,7 +1115,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Re-enable outbound automation disabled during Pre-Migration</t>
+          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1053,12 +1137,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Post Migration</t>
+          <t>Salesforce Config Changes</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spot-check row counts against source</t>
+          <t>Re-enable outbound automation disabled during Pre-Migration</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1073,7 +1157,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1085,20 +1169,47 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>Spot-check row counts against source</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Notify stakeholders the load is complete</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1133,6 +1244,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -914,7 +914,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>040_account_load.sql</t>
+          <t>010_account_load.sql</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -934,12 +934,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-10T22:24:25.093588</t>
+          <t>2026-07-11T15:39:30.796348</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-10T22:24:33.864677</t>
+          <t>2026-07-11T15:39:39.972881</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>050_contact_load.sql</t>
+          <t>020_contact_load.sql</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-10T22:25:23.666209</t>
+          <t>2026-07-11T15:40:40.660607</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-10T22:25:38.022160</t>
+          <t>2026-07-11T15:41:00.551225</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="M21" t="n">
-        <v>738</v>
+        <v>744</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>060_opportunity_load.sql</t>
+          <t>030_opportunity_load.sql</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-10T22:26:17.038396</t>
+          <t>2026-07-11T15:44:01.209609</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-10T22:26:44.202428</t>
+          <t>2026-07-11T15:44:28.744058</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="M22" t="n">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1235,7 +1235,13 @@
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations count="3">
+    <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
+    </dataValidation>
     <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
     </dataValidation>

--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -934,12 +934,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-11T15:39:30.796348</t>
+          <t>2026-07-11T17:38:27.638139</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-11T15:39:39.972881</t>
+          <t>2026-07-11T17:38:36.492095</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="M20" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -988,12 +988,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-11T15:40:40.660607</t>
+          <t>2026-07-11T19:35:30.873591</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-11T15:41:00.551225</t>
+          <t>2026-07-11T19:35:45.181006</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>744</v>
+        <v>446</v>
       </c>
       <c r="M21" t="n">
-        <v>744</v>
+        <v>446</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-11T15:44:01.209609</t>
+          <t>2026-07-11T19:36:25.900677</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-11T15:44:28.744058</t>
+          <t>2026-07-11T19:36:54.189318</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>381</v>
+        <v>230</v>
       </c>
       <c r="M22" t="n">
-        <v>381</v>
+        <v>230</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -1059,80 +1059,114 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>040_task_load.sql</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-11T19:37:56.291523</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-07-11T19:38:12.764338</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #4 (insert, 2 job(s)).</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>530</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>530</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>040_task_load.sql</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-07-11T19:41:24.302042</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-07-11T19:41:45.538388</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #5 (insert, 2 job(s)).</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>530</v>
+      </c>
+      <c r="M24" t="n">
+        <v>530</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Post-Migration Steps</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Salesforce Config Changes</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Re-enable Email Deliverability to its normal setting</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Salesforce Config Changes</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1142,7 +1176,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Re-enable outbound automation disabled during Pre-Migration</t>
+          <t>Re-enable Email Deliverability to its normal setting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1164,12 +1198,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Post Migration</t>
+          <t>Salesforce Config Changes</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spot-check row counts against source</t>
+          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1184,32 +1218,86 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Re-enable outbound automation disabled during Pre-Migration</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Post Migration</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Spot-check row counts against source</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Notify stakeholders the load is complete</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1235,7 +1323,10 @@
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
+    </dataValidation>
     <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
     </dataValidation>
@@ -1252,6 +1343,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -596,6 +596,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -929,7 +930,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Jim Ziller</t>
+          <t>Demo User</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -983,7 +984,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jim Ziller</t>
+          <t>Demo User</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1027,7 +1028,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jim Ziller</t>
+          <t>Demo User</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1071,7 +1072,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jim Ziller</t>
+          <t>Demo User</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1115,7 +1116,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Jim Ziller</t>
+          <t>Demo User</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">

--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dev1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dogfood1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,7 +597,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
@@ -1349,4 +1349,839 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Full Pipeline Dogfood Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Source Environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Target Environment</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D360_PLAYGROUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Git Repository</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Commit / Branch</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ddd8a47b (main)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Scripts (as of this commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration/tree/ddd8a47b7eeac26704d489c233a39b28a87efbfc/sql/transformations</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>JIRA Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Log Id</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Source Ingestion Log Id</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Person Responsible</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Begin Time</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Execution Time</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>JIRA Ticket Link</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Total Records</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Success Records</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Failed Records</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Success Percent</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Error Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pre-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Confirm Email Deliverability setting (Setup &gt; Email Administration &gt; Deliverability)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Disable CPQ/Billing automation (or other managed-package automation) on target objects</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Disable outbound automation that could email real contacts (workflow/Flow email alerts, approval processes)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Confirm target org/alias and auth mode for this pass</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Run analyze-org-risk against in-scope objects</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Take a backup/export of any target data being overwritten</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Source Download and Load Steps</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Load Steps</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>010_account_load.sql</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>5</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>020_contact_load.sql</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>After: Account</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>8</v>
+      </c>
+      <c r="M21" t="n">
+        <v>8</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>030_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>After: Account, Contact</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>13</v>
+      </c>
+      <c r="M22" t="n">
+        <v>13</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>040_task_load.sql</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>After: Account, Contact, Opportunity</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-07-13 11:30</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>27</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Post-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Re-enable Email Deliverability to its normal setting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Re-enable outbound automation disabled during Pre-Migration</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Spot-check row counts against source</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Notify stakeholders the load is complete</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D11:D1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"In Process"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Issue"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E1000">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dev1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dogfood1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postgres1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2184,4 +2185,698 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Full Pipeline Dogfood Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Source Environment</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Target Environment</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D360_PLAYGROUND</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Git Repository</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Commit / Branch</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Scripts (as of this commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>JIRA Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Log Id</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Source Ingestion Log Id</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Person Responsible</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Begin Time</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Execution Time</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>JIRA Ticket Link</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Total Records</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Success Records</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Failed Records</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Success Percent</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Error Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pre-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Confirm Email Deliverability setting (Setup &gt; Email Administration &gt; Deliverability)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Disable CPQ/Billing automation (or other managed-package automation) on target objects</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Disable outbound automation that could email real contacts (workflow/Flow email alerts, approval processes)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Confirm target org/alias and auth mode for this pass</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Run analyze-org-risk against in-scope objects</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Take a backup/export of any target data being overwritten</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Source Download and Load Steps</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Load Steps</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>010_account_load.sql</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>020_contact_load.sql</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>After: Account</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>030_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>After: Account, Contact</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>040_task_load.sql</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>After: Account, Contact, Opportunity</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Post-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Re-enable Email Deliverability to its normal setting</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Re-enable outbound automation disabled during Pre-Migration</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Spot-check row counts against source</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Notify stakeholders the load is complete</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D11:D1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"In Process"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Issue"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E1000">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId6"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dev1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dogfood1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postgres1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPSP_to_NPC_PoC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -68,13 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2251,7 +2255,11 @@
           <t>Git Repository</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2266,7 +2274,11 @@
           <t>Scripts (as of this commit)</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration/tree/ddd8a47b7eeac26704d489c233a39b28a87efbfc/sql/transformations</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2879,4 +2891,1991 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P56"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>NPSP-to-NPC Migration Proof-of-Concept</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Source Environment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NPSP_SOURCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Target Environment</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NPC_TARGET_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Git Repository</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Commit / Branch</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ececcbb6 (feature/npsp-to-npc-migration-poc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Scripts (as of this commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration/tree/ececcbb6bb170384b3fc968fe82f37e62a34e51f/sql/transformations</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>JIRA Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Log Id</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Source Ingestion Log Id</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Person Responsible</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Begin Time</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Execution Time</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>JIRA Ticket Link</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Total Records</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Success Records</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Failed Records</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Success Percent</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Error Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pre-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Confirm Email Deliverability setting (Setup &gt; Email Administration &gt; Deliverability)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Disable CPQ/Billing automation (or other managed-package automation) on target objects</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Disable outbound automation that could email real contacts (workflow/Flow email alerts, approval processes)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Confirm target org/alias and auth mode for this pass</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Run analyze-org-risk against in-scope objects</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Take a backup/export of any target data being overwritten</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Source Download and Load Steps</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Load Steps</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>100_npc_person_account_load.sql</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>None; parallel with: Campaign, GiftDesignation</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>46220.85108469975</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>46220.85120159199</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #11 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>8</v>
+      </c>
+      <c r="M20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>130_npc_campaign_load.sql</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>None; parallel with: Account, GiftDesignation</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>46220.85346695835</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>46220.85357515627</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #15 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GiftDesignation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>None; parallel with: Account, Campaign</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>46220.86490123239</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>46220.86501682271</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #18 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>110_npc_accountcontactrelation_load.sql</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>After: Account; parallel with: CampaignMember, PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>46220.85311335904</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>46220.85322420983</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #13 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>140_npc_campaignmember_load.sql</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>After: Account, Campaign; parallel with: AccountContactRelation, PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>46220.69439351836</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>46220.69450291824</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #6 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>After: Account; parallel with: AccountContactRelation, CampaignMember</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>46220.85328813472</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>46220.85340328974</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #14 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>8</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>8</v>
+      </c>
+      <c r="O25" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>200_npc_gifttransaction_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>After: Account, Campaign, GiftCommitmentSchedule; parallel with: GiftCommitmentSchedule, GiftTransaction, GiftTransactionDesignation</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>46220.69903303896</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>46220.69914156286</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #8 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>190_npc_giftcommitmentschedule_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>After: Campaign, GiftCommitment; parallel with: GiftCommitment, GiftTransaction, GiftTransactionDesignation</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>46220.87238789419</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>46220.87249824835</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #21 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1</v>
+      </c>
+      <c r="O27" s="5" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>210_npc_gifttransaction_from_payment_load.sql</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>After: Account, Campaign, GiftCommitment, GiftCommitmentSchedule; parallel with: GiftCommitment, GiftCommitmentSchedule, GiftTransactionDesignation</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>46220.8843295004</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>46220.88444381276</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #26 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>4</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4</v>
+      </c>
+      <c r="O28" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Load</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>220_npc_gifttransactiondesignation_from_allocation_load.sql</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>After: GiftDesignation, GiftTransaction; parallel with: GiftCommitment, GiftCommitmentSchedule, GiftTransaction</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>46220.88636856332</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>46220.88648058591</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #29 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>8</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8</v>
+      </c>
+      <c r="O29" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>060_contact_load_postgres.sql</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>46217.78807701408</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>46217.78821397861</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #1 (upsert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>8</v>
+      </c>
+      <c r="M30" t="n">
+        <v>8</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>060_contact_load_postgres.sql</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>46220.66804155567</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>46220.66834662133</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #2 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8</v>
+      </c>
+      <c r="O31" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>060_contact_load_postgres.sql</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>46220.66969355435</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>46220.66980037216</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #3 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>8</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>8</v>
+      </c>
+      <c r="O32" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>060_contact_load_postgres.sql</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>46220.68988412705</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>46220.69006023852</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #4 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>npsp__General_Accounting_Unit__c</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>46220.69150847213</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>46220.6916417661</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #5 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>2</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>npe03__Recurring_Donation__c</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>46220.69540090767</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>46220.6955630836</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #7 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>npe01__OppPayment__c</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>46220.70002229994</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>46220.70012346639</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #9 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>5</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>npsp__Allocation__c</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>46220.70092722683</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>46220.70109056849</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #10 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>4</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>100_npc_person_account_load.sql</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>46220.85134134551</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>46220.85145415471</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #12 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PartyRelationshipGroup</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>46220.85554814986</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>46220.8556596904</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #16 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>140_npc_campaignmember_load.sql</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>46220.86407071228</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>46220.86418193246</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #17 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>4</v>
+      </c>
+      <c r="M40" t="n">
+        <v>4</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>180_npc_giftcommitment_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>46220.87122551986</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>46220.87133488774</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #19 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>4</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>4</v>
+      </c>
+      <c r="O41" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>180_npc_giftcommitment_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>46220.87167967914</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>46220.87179699918</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #20 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>4</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>180_npc_giftcommitment_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>46220.87291372754</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>46220.8730268499</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #22 (upsert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>190_npc_giftcommitmentschedule_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>46220.87343585032</v>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>46220.87354344894</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #23 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>4</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3</v>
+      </c>
+      <c r="O44" s="5" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>180_npc_giftcommitment_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>46220.88304505002</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>46220.88315524372</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #24 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>190_npc_giftcommitmentschedule_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>46220.88356825448</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>46220.88367771457</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #25 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>210_npc_gifttransaction_from_payment_load.sql</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>46220.88467559886</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>46220.88478850815</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #27 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>4</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>210_npc_gifttransaction_from_payment_load.sql</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>46220.88533835204</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>46220.88545003521</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #28 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>5</v>
+      </c>
+      <c r="M48" t="n">
+        <v>5</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>220_npc_gifttransactiondesignation_from_allocation_load.sql</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>46220.88689291678</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>46220.88700540022</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #30 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>8</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>8</v>
+      </c>
+      <c r="O49" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>220_npc_gifttransactiondesignation_from_allocation_load.sql</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>46220.88725454533</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>46220.88736506833</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #31 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>8</v>
+      </c>
+      <c r="M50" t="n">
+        <v>8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Post-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n"/>
+      <c r="P51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Re-enable Email Deliverability to its normal setting</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Re-enable outbound automation disabled during Pre-Migration</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Spot-check row counts against source</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Notify stakeholders the load is complete</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D11:D1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"In Process"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Issue"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E1000">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId26"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -2899,7 +2899,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>46220.85108469975</v>
+        <v>46220.85108469908</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>46220.85120159199</v>
+        <v>46220.85120159722</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -3403,10 +3403,10 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>46220.85346695835</v>
+        <v>46220.85346695602</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>46220.85357515627</v>
+        <v>46220.85357516204</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>46220.86490123239</v>
+        <v>46220.86490122685</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>46220.86501682271</v>
+        <v>46220.86501681713</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="G23" s="6" t="n">
-        <v>46220.85311335904</v>
+        <v>46220.85311335648</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>46220.85322420983</v>
+        <v>46220.85322421297</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>46220.69439351836</v>
+        <v>46220.69439351852</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>46220.69450291824</v>
+        <v>46220.69450291667</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3603,10 +3603,10 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>46220.85328813472</v>
+        <v>46220.85328813658</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>46220.85340328974</v>
+        <v>46220.85340328704</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3653,10 +3653,10 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>46220.69903303896</v>
+        <v>46220.69903304398</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>46220.69914156286</v>
+        <v>46220.6991415625</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>46220.87238789419</v>
+        <v>46220.87238789352</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>46220.87249824835</v>
+        <v>46220.87249825231</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -3753,10 +3753,10 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>46220.8843295004</v>
+        <v>46220.88432950232</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>46220.88444381276</v>
+        <v>46220.88444380787</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>46220.88636856332</v>
+        <v>46220.88636856482</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>46220.88648058591</v>
+        <v>46220.88648059028</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>46217.78807701408</v>
+        <v>46217.78807701389</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>46217.78821397861</v>
+        <v>46217.78821398148</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -3883,10 +3883,10 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>46220.66804155567</v>
+        <v>46220.66804155093</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>46220.66834662133</v>
+        <v>46220.66834662037</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="G32" s="6" t="n">
-        <v>46220.66969355435</v>
+        <v>46220.66969355324</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>46220.66980037216</v>
+        <v>46220.66980037037</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -3963,10 +3963,10 @@
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>46220.68988412705</v>
+        <v>46220.68988413194</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>46220.69006023852</v>
+        <v>46220.69006024305</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4003,10 +4003,10 @@
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>46220.69150847213</v>
+        <v>46220.69150847222</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>46220.6916417661</v>
+        <v>46220.69164177083</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4043,10 +4043,10 @@
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>46220.69540090767</v>
+        <v>46220.69540090278</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>46220.6955630836</v>
+        <v>46220.69556307871</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>46220.70002229994</v>
+        <v>46220.70002230324</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>46220.70012346639</v>
+        <v>46220.70012346065</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>46220.70092722683</v>
+        <v>46220.70092722222</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>46220.70109056849</v>
+        <v>46220.70109056713</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>46220.85134134551</v>
+        <v>46220.85134134259</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>46220.85145415471</v>
+        <v>46220.85145415509</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="G39" s="6" t="n">
-        <v>46220.85554814986</v>
+        <v>46220.85554814815</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>46220.8556596904</v>
+        <v>46220.8556596875</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>46220.86407071228</v>
+        <v>46220.86407071759</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>46220.86418193246</v>
+        <v>46220.86418193287</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>46220.87122551986</v>
+        <v>46220.87122552083</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>46220.87133488774</v>
+        <v>46220.87133488426</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -4323,10 +4323,10 @@
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>46220.87167967914</v>
+        <v>46220.87167967593</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>46220.87179699918</v>
+        <v>46220.87179700231</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -4363,10 +4363,10 @@
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>46220.87291372754</v>
+        <v>46220.87291372685</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>46220.8730268499</v>
+        <v>46220.87302685185</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -4403,10 +4403,10 @@
         </is>
       </c>
       <c r="G44" s="6" t="n">
-        <v>46220.87343585032</v>
+        <v>46220.87343584491</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>46220.87354344894</v>
+        <v>46220.87354344907</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>46220.88304505002</v>
+        <v>46220.8830450463</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>46220.88315524372</v>
+        <v>46220.88315524306</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>46220.88356825448</v>
+        <v>46220.88356825231</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>46220.88367771457</v>
+        <v>46220.88367771991</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4523,10 +4523,10 @@
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>46220.88467559886</v>
+        <v>46220.88467560185</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>46220.88478850815</v>
+        <v>46220.88478850694</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>46220.88533835204</v>
+        <v>46220.88533835648</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>46220.88545003521</v>
+        <v>46220.88545003472</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4603,10 +4603,10 @@
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>46220.88689291678</v>
+        <v>46220.88689291666</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>46220.88700540022</v>
+        <v>46220.88700540509</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4643,10 +4643,10 @@
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>46220.88725454533</v>
+        <v>46220.88725454861</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>46220.88736506833</v>
+        <v>46220.88736506944</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4667,157 +4667,397 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>110_npc_accountcontactrelation_load.sql</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>46221.77945109954</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>46221.77960400463</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #32 (delete, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>8</v>
+      </c>
+      <c r="M51" t="n">
+        <v>8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>120_npc_partyrelationshipgroup_load.sql</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>46221.77993625</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>46221.78003027778</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #33 (delete, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>8</v>
+      </c>
+      <c r="M52" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>210_npc_gifttransaction_from_payment_load.sql</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>46221.78038818287</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>46221.78048045139</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #34 (delete, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>4</v>
+      </c>
+      <c r="M53" t="n">
+        <v>4</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>110_npc_accountcontactrelation_load.sql</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>46221.78256820602</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>46221.78267724537</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #35 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>8</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>120_npc_partyrelationshipgroup_load.sql</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>46221.78445824074</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>46221.78456969908</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #36 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>8</v>
+      </c>
+      <c r="M55" t="n">
+        <v>8</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>200_npc_gifttransaction_from_opportunity_load.sql</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Jim Ziller</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>46221.78470510417</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>46221.78481672454</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Auto-synced from dbo.BulkOpsLog #37 (insert, 1 job(s)).</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>4</v>
+      </c>
+      <c r="M56" t="n">
+        <v>4</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>Post-Migration Steps</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-      <c r="O51" s="4" t="n"/>
-      <c r="P51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+      <c r="M57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>Salesforce Config Changes</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Re-enable Email Deliverability to its normal setting</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Salesforce Config Changes</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>Salesforce Config Changes</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Re-enable outbound automation disabled during Pre-Migration</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>Post Migration</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>Spot-check row counts against source</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>Post Migration</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>Notify stakeholders the load is complete</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -4875,6 +5115,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dogfood1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postgres1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPSP_to_NPC_PoC" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Fundraising_Dogfood" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5124,4 +5125,619 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Source Environment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SQL Server: SF_Migration</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Target Environment</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NPC_TARGET_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Git Repository</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Commit / Branch</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>31925f4c (feature/npc-fundraising-dogfood-recipe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Scripts (as of this commit)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jpziller/DataMigration/tree/31925f4cd03106ebf2b0e2001da477830afbc1ef/sql/transformations</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>JIRA Project</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Log Id</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Last Synced Source Ingestion Log Id</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dependency</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Person Responsible</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Begin Time</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>End Time</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Execution Time</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>JIRA Ticket Link</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Total Records</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Success Records</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Failed Records</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Success Percent</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>Error Details</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Pre-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Confirm Email Deliverability setting (Setup &gt; Email Administration &gt; Deliverability)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Disable CPQ/Billing automation (or other managed-package automation) on target objects</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Disable outbound automation that could email real contacts (workflow/Flow email alerts, approval processes)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Confirm target org/alias and auth mode for this pass</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Run analyze-org-risk against in-scope objects</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Pre Migration</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Take a backup/export of any target data being overwritten</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Source Download and Load Steps</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Load Steps</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Post-Migration Steps</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Re-enable Email Deliverability to its normal setting</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Re-enable CPQ/Billing automation (or other managed-package automation)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Salesforce Config Changes</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Re-enable outbound automation disabled during Pre-Migration</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Spot-check row counts against source</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Post Migration</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Notify stakeholders the load is complete</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D11:D1000">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"In Process"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"N/A"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"Completed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Issue"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E11:E1000">
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Yes"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D11:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not Started,N/A,In Process,Completed,Issue"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/migration_run_book.xlsx
+++ b/migration_run_book.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dev1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dogfood1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sample1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postgres1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPSP_to_NPC_PoC" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Fundraising_Dogfood" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NPC_Fundraising_Sample" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Full Pipeline Dogfood Run</t>
+          <t>Full Pipeline Sample Run</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+          <t>Live insert into D360_PLAYGROUND (sample/practice run)</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+          <t>Live insert into D360_PLAYGROUND (sample/practice run)</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+          <t>Live insert into D360_PLAYGROUND (sample/practice run)</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Live insert into D360_PLAYGROUND (dogfood/practice run)</t>
+          <t>Live insert into D360_PLAYGROUND (sample/practice run)</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Full Pipeline Dogfood Run</t>
+          <t>Full Pipeline Sample Run</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31925f4c (feature/npc-fundraising-dogfood-recipe)</t>
+          <t>31925f4c (feature/npc-fundraising-sample-recipe)</t>
         </is>
       </c>
     </row>
